--- a/public/outputs/infosys_valuation_model.xlsx
+++ b/public/outputs/infosys_valuation_model.xlsx
@@ -7,15 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Actuals" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Statement Forecast" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Build" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LBO Debt Schedule" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LBO Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LBO IRR Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Data Scope" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historical Actuals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Statement Forecast" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Build" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF Sensitivity" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LBO Debt Schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LBO Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LBO IRR Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -947,6 +948,250 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Allowed valuation input</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>historical_financials.csv, assumptions.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Last reported actual used by valuation model</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Forecast period</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FY2026-FY2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Excluded from valuation inputs and tuning</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fy2026_actuals.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FY2026 actuals usage</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Back-test validation only; not used to set, fit, or tune model assumptions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>10.0x Exit</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>11.0x Exit</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>12.0x Exit</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>13.0x Exit</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>14.0x Exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.0196989050159968</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.03932288450150323</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.05756775828783911</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.07463411494228156</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.09068052892060163</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.02902128691984229</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.04882467449369421</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.0672363481857543</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.08445873040191643</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.1006518453314262</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.03887961327772183</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.0588727231247439</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.07746078606196183</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.09484816376141003</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.1111964134910983</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0.04933322423738296</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.06952751253621337</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.08830261579644438</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0.1058649520567843</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.1223777042373451</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.05099780482056748</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.07211451613845887</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.09168775630810688</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.1099502739450793</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.1270844118488463</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1227,7 +1472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1789,7 +2034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2101,7 +2346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2223,7 +2468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2353,7 +2598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2549,7 +2794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2776,7 +3021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2894,158 +3139,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Debt / EBITDA</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>10.0x Exit</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>11.0x Exit</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>12.0x Exit</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>13.0x Exit</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>14.0x Exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>0.0196989050159968</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0.03932288450150323</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0.05756775828783911</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.07463411494228156</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.09068052892060163</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.02902128691984229</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.04882467449369421</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.0672363481857543</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.08445873040191643</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.1006518453314262</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>0.03887961327772183</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0.0588727231247439</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>0.07746078606196183</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.09484816376141003</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>0.1111964134910983</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0.04933322423738296</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0.06952751253621337</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.08830261579644438</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.1058649520567843</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0.1223777042373451</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.05099780482056748</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0.07211451613845887</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.09168775630810688</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0.1099502739450793</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0.1270844118488463</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>